--- a/Inventory.xlsx
+++ b/Inventory.xlsx
@@ -1,43 +1,445 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MTECH\7_SEMESTER\Introduction to DevOps\Assignment\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCCB8B40-973C-4ACE-9D6B-BA38B46CCCA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1313BAE7-BF3E-4337-909E-8014FD150BA7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="play_tennis" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="32">
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>outlook</t>
+  </si>
+  <si>
+    <t>temp</t>
+  </si>
+  <si>
+    <t>humidity</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>play</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>Sunny</t>
+  </si>
+  <si>
+    <t>Hot</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Weak</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>Strong</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>Overcast</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>Rain</t>
+  </si>
+  <si>
+    <t>Mild</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>Cool</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>D9</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>D11</t>
+  </si>
+  <si>
+    <t>D12</t>
+  </si>
+  <si>
+    <t>D13</t>
+  </si>
+  <si>
+    <t>D14</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -45,15 +447,204 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -79,39 +670,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -144,9 +735,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -179,6 +787,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -240,13 +865,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -255,6 +873,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -319,21 +944,345 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F48D020-19E5-4847-AE25-3EC3D02BB14C}">
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>